--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="144">
   <si>
     <t>职业ID</t>
   </si>
@@ -61,6 +61,9 @@
     <t>近战前摇</t>
   </si>
   <si>
+    <t>远程前摇停顿帧</t>
+  </si>
+  <si>
     <t>远程弹速</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>士兵简画图标</t>
   </si>
   <si>
+    <t>普通攻击动作</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
     <t>UI-033 战斗指示器简画；仅文件名；Resources/UI/Icons/{Id}；空=空框</t>
   </si>
   <si>
+    <t>动作ID;权重|动作ID;权重；每次普攻按权重随机1个基名；空/非法/当前朝向无状态则Attack1；不参与伤害</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
@@ -169,6 +178,9 @@
     <t>MeleeWindupSeconds</t>
   </si>
   <si>
+    <t>RangedWindupHoldFrame</t>
+  </si>
+  <si>
     <t>RangedProjectileSpeed</t>
   </si>
   <si>
@@ -196,6 +208,9 @@
     <t>SilhouetteIconAssetId</t>
   </si>
   <si>
+    <t>NormalAttackAnims</t>
+  </si>
+  <si>
     <t>Class_BaseWarrior</t>
   </si>
   <si>
@@ -229,6 +244,9 @@
     <t>HPPK_UI_Class_BaseWarrior</t>
   </si>
   <si>
+    <t>Attack1;1|Attack2;1</t>
+  </si>
+  <si>
     <t>Class_BaseArcher</t>
   </si>
   <si>
@@ -244,9 +262,6 @@
     <t>NormalAttackPrimaryMult_1|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>Ranged</t>
   </si>
   <si>
@@ -256,6 +271,9 @@
     <t>HPPK_UI_Class_BaseArcher</t>
   </si>
   <si>
+    <t>Attack3;1</t>
+  </si>
+  <si>
     <t>Class_BaseMage</t>
   </si>
   <si>
@@ -268,16 +286,13 @@
     <t>Intelligence</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>App_0_20</t>
   </si>
   <si>
     <t>HPPK_UI_Class_BaseMage</t>
+  </si>
+  <si>
+    <t>Attack5;1</t>
   </si>
   <si>
     <t>Class_BaseRogue</t>
@@ -936,148 +951,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1444,19 +1459,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.45454545454546" customWidth="1"/>
+    <col min="4" max="4" width="15.4545454545455" style="2" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="23.25" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="7" max="7" width="23.2727272727273" customWidth="1"/>
+    <col min="8" max="8" width="9.54545454545454" customWidth="1"/>
+    <col min="9" max="10" width="10.1818181818182" customWidth="1"/>
+    <col min="11" max="11" width="10.2727272727273" customWidth="1"/>
+    <col min="12" max="12" width="10.7272727272727" customWidth="1"/>
+    <col min="13" max="13" width="8.45454545454546" customWidth="1"/>
+    <col min="14" max="14" width="9.36363636363636" customWidth="1"/>
+    <col min="19" max="19" width="28.0909090909091" customWidth="1"/>
+    <col min="20" max="20" width="20.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1511,1092 +1532,1215 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" t="s">
+        <v>51</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R3" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:18">
+    <row r="4" ht="14.25" customHeight="1" spans="1:20">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H4" s="2">
         <v>0.35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4">
+        <v>65</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4">
         <v>1.2</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1.1</v>
       </c>
-      <c r="N4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="R4" t="s">
-        <v>64</v>
+      <c r="O4" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T4" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:18">
+    <row r="5" ht="14.25" customHeight="1" spans="1:20">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2">
+        <v>8</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5">
+      <c r="M5">
         <v>1.2</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="5">
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="5">
         <v>4</v>
       </c>
-      <c r="P5" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="R5" t="s">
-        <v>73</v>
+      <c r="Q5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="S5" t="s">
+        <v>78</v>
+      </c>
+      <c r="T5" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:18">
+    <row r="6" ht="14.25" customHeight="1" spans="1:20">
       <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>10</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6">
+        <v>1.2</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="S6" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1" spans="1:20">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="G7" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6">
-        <v>1.2</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="5">
-        <v>3</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="R6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:18">
-      <c r="A7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="H7" s="2">
         <v>0.35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7">
         <v>1.2</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1.15</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="S7" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:20">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
         <v>61</v>
       </c>
-      <c r="O7" s="5">
-        <v>2</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:18">
-      <c r="A8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8">
+        <v>1.2</v>
+      </c>
+      <c r="N8">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="R8" t="s">
+        <v>95</v>
+      </c>
+      <c r="S8" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8">
-        <v>1.2</v>
-      </c>
-      <c r="M8">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>90</v>
-      </c>
-      <c r="R8" t="s">
-        <v>64</v>
+      <c r="T8" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:18">
+    <row r="9" ht="14.25" customHeight="1" spans="1:20">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9">
+        <v>75</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2">
+        <v>8</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9">
         <v>1.2</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" s="5">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P9" s="5">
         <v>4</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>93</v>
+      <c r="Q9" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="R9" t="s">
-        <v>73</v>
+        <v>98</v>
+      </c>
+      <c r="S9" t="s">
+        <v>78</v>
+      </c>
+      <c r="T9" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:18">
+    <row r="10" ht="14.25" customHeight="1" spans="1:20">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10">
+        <v>75</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2">
+        <v>5</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10">
         <v>1.2</v>
       </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="5">
         <v>3</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>96</v>
+      <c r="Q10" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="R10" t="s">
-        <v>81</v>
+        <v>101</v>
+      </c>
+      <c r="S10" t="s">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:18">
+    <row r="11" ht="14.25" customHeight="1" spans="1:20">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2">
         <v>0.35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11">
+        <v>65</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11">
         <v>1.2</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1.15</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O11" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="R11" t="s">
+        <v>104</v>
+      </c>
+      <c r="S11" t="s">
+        <v>91</v>
+      </c>
+      <c r="T11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:20">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="O11" s="5">
-        <v>2</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>99</v>
-      </c>
-      <c r="R11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:18">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E12" s="2">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2">
         <v>0.35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12">
         <v>1.2</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>61</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>103</v>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>66</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="R12" t="s">
-        <v>64</v>
+        <v>108</v>
+      </c>
+      <c r="S12" t="s">
+        <v>69</v>
+      </c>
+      <c r="T12" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1" spans="1:18">
+    <row r="13" ht="14.25" customHeight="1" spans="1:20">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E13" s="2">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13">
+        <v>75</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>10</v>
+      </c>
+      <c r="K13" s="2">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
         <v>1.2</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
-        <v>71</v>
-      </c>
-      <c r="O13" s="5">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="5">
         <v>4</v>
       </c>
-      <c r="P13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>107</v>
+      <c r="Q13" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="R13" t="s">
-        <v>73</v>
+        <v>112</v>
+      </c>
+      <c r="S13" t="s">
+        <v>78</v>
+      </c>
+      <c r="T13" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:18">
+    <row r="14" ht="14.25" customHeight="1" spans="1:20">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E14" s="2">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L14">
+        <v>75</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>10</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14">
         <v>1.2</v>
       </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14" t="s">
-        <v>71</v>
-      </c>
-      <c r="O14" s="5">
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="5">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>111</v>
+      <c r="Q14" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="R14" t="s">
-        <v>81</v>
+        <v>116</v>
+      </c>
+      <c r="S14" t="s">
+        <v>85</v>
+      </c>
+      <c r="T14" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:18">
+    <row r="15" ht="14.25" customHeight="1" spans="1:20">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E15" s="2">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2">
         <v>0.35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15">
+        <v>65</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15">
         <v>1.2</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>1.15</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
+        <v>66</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="R15" t="s">
+        <v>120</v>
+      </c>
+      <c r="S15" t="s">
+        <v>91</v>
+      </c>
+      <c r="T15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" spans="1:20">
+      <c r="A16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" t="s">
         <v>61</v>
       </c>
-      <c r="O15" s="5">
-        <v>2</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>115</v>
-      </c>
-      <c r="R15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1" spans="1:18">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2">
         <v>0.35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16">
+        <v>65</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16">
         <v>1.2</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1.1</v>
       </c>
-      <c r="N16" t="s">
-        <v>61</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>119</v>
+      <c r="O16" t="s">
+        <v>66</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="R16" t="s">
-        <v>64</v>
+        <v>124</v>
+      </c>
+      <c r="S16" t="s">
+        <v>69</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:18">
+    <row r="17" ht="14.25" customHeight="1" spans="1:20">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L17">
+        <v>75</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17">
         <v>1.2</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>71</v>
-      </c>
-      <c r="O17" s="5">
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="5">
         <v>4</v>
       </c>
-      <c r="P17" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>123</v>
+      <c r="Q17" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="R17" t="s">
-        <v>73</v>
+        <v>128</v>
+      </c>
+      <c r="S17" t="s">
+        <v>78</v>
+      </c>
+      <c r="T17" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1" spans="1:18">
+    <row r="18" ht="14.25" customHeight="1" spans="1:20">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E18" s="2">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>10</v>
+      </c>
+      <c r="K18" s="2">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18">
         <v>1.2</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="s">
-        <v>71</v>
-      </c>
-      <c r="O18" s="5">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>76</v>
+      </c>
+      <c r="P18" s="5">
         <v>3</v>
       </c>
-      <c r="P18" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>127</v>
+      <c r="Q18" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="R18" t="s">
-        <v>81</v>
+        <v>132</v>
+      </c>
+      <c r="S18" t="s">
+        <v>85</v>
+      </c>
+      <c r="T18" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="1:18">
+    <row r="19" ht="14.25" customHeight="1" spans="1:20">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E19" s="2">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2">
         <v>0.35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19">
         <v>1.2</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>1.15</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" s="5">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="R19" t="s">
+        <v>136</v>
+      </c>
+      <c r="S19" t="s">
+        <v>91</v>
+      </c>
+      <c r="T19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
         <v>61</v>
       </c>
-      <c r="O19" s="5">
-        <v>2</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>131</v>
-      </c>
-      <c r="R19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E20" s="2">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20">
+        <v>1.2</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="R20" t="s">
+        <v>140</v>
+      </c>
+      <c r="S20" t="s">
         <v>69</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20">
-        <v>1.2</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20" t="s">
-        <v>61</v>
-      </c>
-      <c r="O20" s="5">
-        <v>1</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>135</v>
-      </c>
-      <c r="R20" t="s">
-        <v>64</v>
+      <c r="T20" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:18">
+    <row r="21" ht="14.25" customHeight="1" spans="1:20">
       <c r="A21" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="L21">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10</v>
+      </c>
+      <c r="K21" s="2">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21">
         <v>1.2</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
-        <v>71</v>
-      </c>
-      <c r="O21" s="5">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="5">
         <v>2</v>
       </c>
-      <c r="P21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>135</v>
+      <c r="Q21" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="R21" t="s">
-        <v>81</v>
+        <v>140</v>
+      </c>
+      <c r="S21" t="s">
+        <v>85</v>
+      </c>
+      <c r="T21" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1695,10 +1695,10 @@
         <v>65</v>
       </c>
       <c r="M4">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="s">
         <v>66</v>
@@ -1751,10 +1751,10 @@
         <v>67</v>
       </c>
       <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
         <v>1.2</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
       </c>
       <c r="O5" t="s">
         <v>76</v>
@@ -1807,10 +1807,10 @@
         <v>67</v>
       </c>
       <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
         <v>1.2</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
       </c>
       <c r="O6" t="s">
         <v>76</v>
@@ -1863,10 +1863,10 @@
         <v>65</v>
       </c>
       <c r="M7">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="s">
         <v>66</v>
@@ -1919,10 +1919,10 @@
         <v>65</v>
       </c>
       <c r="M8">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="s">
         <v>66</v>
@@ -1978,10 +1978,10 @@
         <v>67</v>
       </c>
       <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
         <v>1.2</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
       </c>
       <c r="O9" t="s">
         <v>76</v>
@@ -2037,10 +2037,10 @@
         <v>67</v>
       </c>
       <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
         <v>1.2</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
       </c>
       <c r="O10" t="s">
         <v>76</v>
@@ -2099,10 +2099,10 @@
         <v>65</v>
       </c>
       <c r="M11">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="s">
         <v>66</v>
@@ -2161,10 +2161,10 @@
         <v>65</v>
       </c>
       <c r="M12">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="s">
         <v>66</v>
@@ -2223,10 +2223,10 @@
         <v>67</v>
       </c>
       <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>1.2</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
       </c>
       <c r="O13" t="s">
         <v>76</v>
@@ -2285,10 +2285,10 @@
         <v>67</v>
       </c>
       <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
         <v>1.2</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
       </c>
       <c r="O14" t="s">
         <v>76</v>
@@ -2347,10 +2347,10 @@
         <v>65</v>
       </c>
       <c r="M15">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N15">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="s">
         <v>66</v>
@@ -2409,10 +2409,10 @@
         <v>65</v>
       </c>
       <c r="M16">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="s">
         <v>66</v>
@@ -2471,10 +2471,10 @@
         <v>67</v>
       </c>
       <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
         <v>1.2</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
       </c>
       <c r="O17" t="s">
         <v>76</v>
@@ -2533,10 +2533,10 @@
         <v>67</v>
       </c>
       <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
         <v>1.2</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
       </c>
       <c r="O18" t="s">
         <v>76</v>
@@ -2595,10 +2595,10 @@
         <v>65</v>
       </c>
       <c r="M19">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="s">
         <v>66</v>
@@ -2657,10 +2657,10 @@
         <v>65</v>
       </c>
       <c r="M20">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="s">
         <v>66</v>
@@ -2719,10 +2719,10 @@
         <v>67</v>
       </c>
       <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
         <v>1.2</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
       </c>
       <c r="O21" t="s">
         <v>76</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="144">
   <si>
     <t>职业ID</t>
   </si>
@@ -241,6 +241,9 @@
     <t>App_0_00</t>
   </si>
   <si>
+    <t>Skill_Form_Wedge_02</t>
+  </si>
+  <si>
     <t>HPPK_UI_Class_BaseWarrior</t>
   </si>
   <si>
@@ -319,7 +322,7 @@
     <t>App_0_01</t>
   </si>
   <si>
-    <t>Skill_01</t>
+    <t>Skill_01|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Archer</t>
@@ -328,7 +331,7 @@
     <t>App_0_11</t>
   </si>
   <si>
-    <t>Skill_02</t>
+    <t>Skill_02|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Mage</t>
@@ -337,7 +340,7 @@
     <t>App_0_21</t>
   </si>
   <si>
-    <t>Skill_03</t>
+    <t>Skill_03|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Rogue</t>
@@ -346,7 +349,7 @@
     <t>App_0_31</t>
   </si>
   <si>
-    <t>Skill_04</t>
+    <t>Skill_04|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Guardian</t>
@@ -358,7 +361,7 @@
     <t>App_0_02</t>
   </si>
   <si>
-    <t>Skill_05</t>
+    <t>Skill_05|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_BombMaster</t>
@@ -370,7 +373,7 @@
     <t>App_0_12</t>
   </si>
   <si>
-    <t>Skill_06</t>
+    <t>Skill_06|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_IceMage</t>
@@ -382,7 +385,7 @@
     <t>App_0_22</t>
   </si>
   <si>
-    <t>Skill_07</t>
+    <t>Skill_07|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Brawler</t>
@@ -394,7 +397,7 @@
     <t>App_0_32</t>
   </si>
   <si>
-    <t>Skill_08</t>
+    <t>Skill_08|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Berserker</t>
@@ -406,7 +409,7 @@
     <t>App_0_03</t>
   </si>
   <si>
-    <t>Skill_09</t>
+    <t>Skill_09|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Longbowman</t>
@@ -418,7 +421,7 @@
     <t>App_0_13</t>
   </si>
   <si>
-    <t>Skill_10</t>
+    <t>Skill_10|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_FireMage</t>
@@ -430,7 +433,7 @@
     <t>App_0_23</t>
   </si>
   <si>
-    <t>Skill_11</t>
+    <t>Skill_11|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Shadowblade</t>
@@ -442,7 +445,7 @@
     <t>App_0_33</t>
   </si>
   <si>
-    <t>Skill_12</t>
+    <t>Skill_12|Skill_Form_Wedge_02</t>
   </si>
   <si>
     <t>Class_Paladin</t>
@@ -452,9 +455,6 @@
   </si>
   <si>
     <t>App_4_41</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Class_DarkMage</t>
@@ -1473,6 +1473,7 @@
     <col min="12" max="12" width="10.7272727272727" customWidth="1"/>
     <col min="13" max="13" width="8.45454545454546" customWidth="1"/>
     <col min="14" max="14" width="9.36363636363636" customWidth="1"/>
+    <col min="18" max="18" width="19.9090909090909" customWidth="1"/>
     <col min="19" max="19" width="28.0909090909091" customWidth="1"/>
     <col min="20" max="20" width="20.2727272727273" customWidth="1"/>
   </cols>
@@ -1709,31 +1710,34 @@
       <c r="Q4" s="6" t="s">
         <v>68</v>
       </c>
+      <c r="R4" t="s">
+        <v>69</v>
+      </c>
       <c r="S4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:20">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2">
         <v>1.5</v>
@@ -1757,39 +1761,42 @@
         <v>1.2</v>
       </c>
       <c r="O5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5" s="5">
         <v>4</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>69</v>
       </c>
       <c r="S5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1" spans="1:20">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1813,39 +1820,42 @@
         <v>1.2</v>
       </c>
       <c r="O6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P6" s="5">
         <v>3</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R6" t="s">
+        <v>69</v>
       </c>
       <c r="S6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1" spans="1:20">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2">
         <v>0.35</v>
@@ -1875,18 +1885,21 @@
         <v>2</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R7" t="s">
+        <v>69</v>
       </c>
       <c r="S7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:20">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
@@ -1901,10 +1914,10 @@
         <v>62</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>64</v>
@@ -1931,36 +1944,36 @@
         <v>67</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:20">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2">
         <v>1.5</v>
@@ -1984,42 +1997,42 @@
         <v>1.2</v>
       </c>
       <c r="O9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P9" s="5">
         <v>4</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:20">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -2043,45 +2056,45 @@
         <v>1.2</v>
       </c>
       <c r="O10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P10" s="5">
         <v>3</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:20">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2">
         <v>0.35</v>
@@ -2111,30 +2124,30 @@
         <v>2</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:20">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="2">
         <v>3</v>
@@ -2143,7 +2156,7 @@
         <v>62</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2">
         <v>0.35</v>
@@ -2173,39 +2186,39 @@
         <v>67</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:20">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2">
         <v>1.5</v>
@@ -2229,45 +2242,45 @@
         <v>1.2</v>
       </c>
       <c r="O13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P13" s="5">
         <v>4</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:20">
       <c r="A14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" s="2">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2291,36 +2304,36 @@
         <v>1.2</v>
       </c>
       <c r="O14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P14" s="5">
         <v>3</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:20">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="2">
         <v>3</v>
@@ -2329,7 +2342,7 @@
         <v>62</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2">
         <v>0.35</v>
@@ -2359,30 +2372,30 @@
         <v>2</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:20">
       <c r="A16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
         <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -2391,7 +2404,7 @@
         <v>62</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2">
         <v>0.35</v>
@@ -2421,39 +2434,39 @@
         <v>67</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:20">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2">
         <v>1.5</v>
@@ -2477,45 +2490,45 @@
         <v>1.2</v>
       </c>
       <c r="O17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P17" s="5">
         <v>4</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:20">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2539,45 +2552,45 @@
         <v>1.2</v>
       </c>
       <c r="O18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="5">
         <v>3</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:20">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E19" s="2">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2">
         <v>0.35</v>
@@ -2607,30 +2620,30 @@
         <v>2</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
         <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2">
         <v>4</v>
@@ -2639,7 +2652,7 @@
         <v>62</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>64</v>
@@ -2669,16 +2682,16 @@
         <v>1</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R20" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="S20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:20">
@@ -2689,7 +2702,7 @@
         <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>142</v>
@@ -2698,10 +2711,10 @@
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2725,7 +2738,7 @@
         <v>1.2</v>
       </c>
       <c r="O21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="5">
         <v>2</v>
@@ -2734,13 +2747,13 @@
         <v>143</v>
       </c>
       <c r="R21" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="S21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="157">
   <si>
     <t>职业ID</t>
   </si>
@@ -94,6 +94,24 @@
     <t>普通攻击动作</t>
   </si>
   <si>
+    <t>特殊普通攻击动作</t>
+  </si>
+  <si>
+    <t>抛物线近战距离</t>
+  </si>
+  <si>
+    <t>抛物线起始距离</t>
+  </si>
+  <si>
+    <t>抛物线命中率</t>
+  </si>
+  <si>
+    <t>未命中落点超出</t>
+  </si>
+  <si>
+    <t>未命中停留秒</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
@@ -121,6 +139,9 @@
     <t>≥0 秒；Melee 时用</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>≥0；Ranged 时用</t>
   </si>
   <si>
@@ -151,6 +172,24 @@
     <t>动作ID;权重|动作ID;权重；每次普攻按权重随机1个基名；空/非法/当前朝向无状态则Attack1；不参与伤害</t>
   </si>
   <si>
+    <t>Parabola临时近战普攻动作权重池；编码同NormalAttackAnims；空→Attack1；非Parabola可空</t>
+  </si>
+  <si>
+    <t>XZ center; forward-arc enemy closer than this uses temporary melee; default 0.25</t>
+  </si>
+  <si>
+    <t>Target center distance that starts the arc and hit roll; default 1.25</t>
+  </si>
+  <si>
+    <t>0 to 1; rolled once at fire; default 0.6</t>
+  </si>
+  <si>
+    <t>Miss lands this far behind the target along aim; default 0.8</t>
+  </si>
+  <si>
+    <t>Seconds a miss stays on the ground; default 1.5</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
@@ -211,6 +250,24 @@
     <t>NormalAttackAnims</t>
   </si>
   <si>
+    <t>ParabolaMeleeAttackAnims</t>
+  </si>
+  <si>
+    <t>ParabolaMeleeRange</t>
+  </si>
+  <si>
+    <t>ParabolaArcMinDistance</t>
+  </si>
+  <si>
+    <t>ParabolaHitRate</t>
+  </si>
+  <si>
+    <t>ParabolaMissOvershoot</t>
+  </si>
+  <si>
+    <t>ParabolaMissLingerSeconds</t>
+  </si>
+  <si>
     <t>Class_BaseWarrior</t>
   </si>
   <si>
@@ -241,7 +298,7 @@
     <t>App_0_00</t>
   </si>
   <si>
-    <t>Skill_Form_Wedge_02</t>
+    <t>Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>HPPK_UI_Class_BaseWarrior</t>
@@ -265,30 +322,30 @@
     <t>NormalAttackPrimaryMult_1|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
   </si>
   <si>
+    <t>Parabola</t>
+  </si>
+  <si>
+    <t>Attack3;1</t>
+  </si>
+  <si>
+    <t>Attack1;1</t>
+  </si>
+  <si>
+    <t>Class_BaseMage</t>
+  </si>
+  <si>
+    <t>枯骨法师</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
     <t>Ranged</t>
   </si>
   <si>
-    <t>App_0_10</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Class_BaseArcher</t>
-  </si>
-  <si>
-    <t>Attack3;1</t>
-  </si>
-  <si>
-    <t>Class_BaseMage</t>
-  </si>
-  <si>
-    <t>枯骨法师</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
     <t>App_0_20</t>
   </si>
   <si>
@@ -322,25 +379,19 @@
     <t>App_0_01</t>
   </si>
   <si>
-    <t>Skill_01|Skill_Form_Wedge_02</t>
+    <t>Skill_01|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Archer</t>
   </si>
   <si>
-    <t>App_0_11</t>
-  </si>
-  <si>
-    <t>Skill_02|Skill_Form_Wedge_02</t>
-  </si>
-  <si>
     <t>Class_Mage</t>
   </si>
   <si>
     <t>App_0_21</t>
   </si>
   <si>
-    <t>Skill_03|Skill_Form_Wedge_02</t>
+    <t>Skill_03|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Rogue</t>
@@ -349,7 +400,7 @@
     <t>App_0_31</t>
   </si>
   <si>
-    <t>Skill_04|Skill_Form_Wedge_02</t>
+    <t>Skill_04|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Guardian</t>
@@ -361,7 +412,7 @@
     <t>App_0_02</t>
   </si>
   <si>
-    <t>Skill_05|Skill_Form_Wedge_02</t>
+    <t>Skill_05|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_BombMaster</t>
@@ -370,12 +421,6 @@
     <t>炸弹师</t>
   </si>
   <si>
-    <t>App_0_12</t>
-  </si>
-  <si>
-    <t>Skill_06|Skill_Form_Wedge_02</t>
-  </si>
-  <si>
     <t>Class_IceMage</t>
   </si>
   <si>
@@ -385,7 +430,7 @@
     <t>App_0_22</t>
   </si>
   <si>
-    <t>Skill_07|Skill_Form_Wedge_02</t>
+    <t>Skill_07|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Brawler</t>
@@ -397,7 +442,7 @@
     <t>App_0_32</t>
   </si>
   <si>
-    <t>Skill_08|Skill_Form_Wedge_02</t>
+    <t>Skill_08|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Berserker</t>
@@ -409,7 +454,7 @@
     <t>App_0_03</t>
   </si>
   <si>
-    <t>Skill_09|Skill_Form_Wedge_02</t>
+    <t>Skill_09|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Longbowman</t>
@@ -418,12 +463,6 @@
     <t>长弓手</t>
   </si>
   <si>
-    <t>App_0_13</t>
-  </si>
-  <si>
-    <t>Skill_10|Skill_Form_Wedge_02</t>
-  </si>
-  <si>
     <t>Class_FireMage</t>
   </si>
   <si>
@@ -433,7 +472,7 @@
     <t>App_0_23</t>
   </si>
   <si>
-    <t>Skill_11|Skill_Form_Wedge_02</t>
+    <t>Skill_11|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Shadowblade</t>
@@ -445,7 +484,7 @@
     <t>App_0_33</t>
   </si>
   <si>
-    <t>Skill_12|Skill_Form_Wedge_02</t>
+    <t>Skill_12|Skill_Form_Wedge_01|Skill_Form_Wedge_02|Skill_Form_Wedge_03|Skill_Form_Wedge_04</t>
   </si>
   <si>
     <t>Class_Paladin</t>
@@ -478,14 +517,14 @@
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -636,7 +675,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -646,12 +685,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -951,19 +984,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -972,7 +1005,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -996,16 +1029,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1014,104 +1047,93 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1165,7 +1187,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1249,6 +1271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1283,6 +1306,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1317,20 +1341,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1452,33 +1472,61 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="9.45454545454546" customWidth="1"/>
-    <col min="4" max="4" width="15.4545454545455" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="23.2727272727273" customWidth="1"/>
-    <col min="8" max="8" width="9.54545454545454" customWidth="1"/>
-    <col min="9" max="10" width="10.1818181818182" customWidth="1"/>
-    <col min="11" max="11" width="10.2727272727273" customWidth="1"/>
-    <col min="12" max="12" width="10.7272727272727" customWidth="1"/>
-    <col min="13" max="13" width="8.45454545454546" customWidth="1"/>
-    <col min="14" max="14" width="9.36363636363636" customWidth="1"/>
-    <col min="18" max="18" width="19.9090909090909" customWidth="1"/>
-    <col min="19" max="19" width="28.0909090909091" customWidth="1"/>
-    <col min="20" max="20" width="20.2727272727273" customWidth="1"/>
+    <col min="18" max="18" width="24.3333333333333" customWidth="1"/>
+    <col min="20" max="20" width="22.5" customWidth="1"/>
+    <col min="21" max="21" width="17.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1539,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1539,208 +1587,289 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:20">
+    <row r="3" s="1" customFormat="1" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" t="s">
-        <v>58</v>
+        <v>69</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:20">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="2">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>63</v>
+        <v>81</v>
+      </c>
+      <c r="G4" t="s">
+        <v>82</v>
       </c>
       <c r="H4" s="2">
         <v>0.35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M4">
+        <v>84</v>
+      </c>
+      <c r="M4" s="2">
         <v>1.1</v>
       </c>
       <c r="N4">
         <v>1.5</v>
       </c>
       <c r="O4" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="P4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>87</v>
       </c>
       <c r="R4" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S4" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="T4" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U4" t="s">
+        <v>35</v>
+      </c>
+      <c r="V4" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" t="s">
+        <v>35</v>
+      </c>
+      <c r="X4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:20">
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="2">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="G5" t="s">
+        <v>95</v>
       </c>
       <c r="H5" s="2">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1752,51 +1881,72 @@
         <v>8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M5">
+        <v>86</v>
+      </c>
+      <c r="M5" s="2">
         <v>1</v>
       </c>
       <c r="N5">
         <v>1.2</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="5">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>78</v>
+        <v>96</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S5" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="T5" t="s">
-        <v>80</v>
+        <v>97</v>
+      </c>
+      <c r="U5" t="s">
+        <v>98</v>
+      </c>
+      <c r="V5">
+        <v>0.5</v>
+      </c>
+      <c r="W5">
+        <v>1.75</v>
+      </c>
+      <c r="X5">
+        <v>0.6</v>
+      </c>
+      <c r="Y5">
+        <v>0.8</v>
+      </c>
+      <c r="Z5">
+        <v>1.5</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:20">
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="2">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G6" t="s">
+        <v>95</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1811,172 +1961,235 @@
         <v>5</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6">
+        <v>86</v>
+      </c>
+      <c r="M6" s="2">
         <v>1</v>
       </c>
       <c r="N6">
         <v>1.2</v>
       </c>
       <c r="O6" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" s="5">
+        <v>103</v>
+      </c>
+      <c r="P6">
         <v>3</v>
       </c>
-      <c r="Q6" s="6" t="s">
-        <v>85</v>
+      <c r="Q6" t="s">
+        <v>104</v>
       </c>
       <c r="R6" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S6" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T6" t="s">
-        <v>87</v>
+        <v>106</v>
+      </c>
+      <c r="U6" t="s">
+        <v>35</v>
+      </c>
+      <c r="V6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" t="s">
+        <v>35</v>
+      </c>
+      <c r="X6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:20">
+    <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="2">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="G7" t="s">
+        <v>95</v>
       </c>
       <c r="H7" s="2">
         <v>0.35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7">
+        <v>84</v>
+      </c>
+      <c r="M7" s="2">
         <v>1.1</v>
       </c>
       <c r="N7">
         <v>1.5</v>
       </c>
       <c r="O7" t="s">
-        <v>66</v>
-      </c>
-      <c r="P7" s="5">
+        <v>85</v>
+      </c>
+      <c r="P7">
         <v>2</v>
       </c>
-      <c r="Q7" s="6" t="s">
-        <v>91</v>
+      <c r="Q7" t="s">
+        <v>110</v>
       </c>
       <c r="R7" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S7" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="T7" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U7" t="s">
+        <v>35</v>
+      </c>
+      <c r="V7" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:20">
+    <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="2">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8">
+        <v>84</v>
+      </c>
+      <c r="M8" s="2">
         <v>1.1</v>
       </c>
       <c r="N8">
         <v>1.5</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R8" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" t="s">
+        <v>89</v>
+      </c>
+      <c r="T8" t="s">
+        <v>90</v>
+      </c>
+      <c r="U8" t="s">
+        <v>35</v>
+      </c>
+      <c r="V8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" t="s">
         <v>95</v>
       </c>
-      <c r="R8" t="s">
-        <v>96</v>
-      </c>
-      <c r="S8" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:20">
-      <c r="A9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="H9" s="2">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -1988,51 +2201,72 @@
         <v>8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9">
+        <v>86</v>
+      </c>
+      <c r="M9" s="2">
         <v>1</v>
       </c>
       <c r="N9">
         <v>1.2</v>
       </c>
       <c r="O9" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" s="5">
-        <v>4</v>
-      </c>
-      <c r="Q9" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>88</v>
+      </c>
+      <c r="S9" t="s">
+        <v>35</v>
+      </c>
+      <c r="T9" t="s">
+        <v>97</v>
+      </c>
+      <c r="U9" t="s">
         <v>98</v>
       </c>
-      <c r="R9" t="s">
-        <v>99</v>
-      </c>
-      <c r="S9" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" t="s">
-        <v>80</v>
+      <c r="V9">
+        <v>0.5</v>
+      </c>
+      <c r="W9">
+        <v>1.75</v>
+      </c>
+      <c r="X9">
+        <v>0.6</v>
+      </c>
+      <c r="Y9">
+        <v>0.8</v>
+      </c>
+      <c r="Z9">
+        <v>1.5</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:20">
+    <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="2">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -2047,178 +2281,229 @@
         <v>5</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10">
+        <v>86</v>
+      </c>
+      <c r="M10" s="2">
         <v>1</v>
       </c>
       <c r="N10">
         <v>1.2</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" s="5">
+        <v>103</v>
+      </c>
+      <c r="P10">
         <v>3</v>
       </c>
-      <c r="Q10" s="6" t="s">
-        <v>101</v>
+      <c r="Q10" t="s">
+        <v>118</v>
       </c>
       <c r="R10" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="S10" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T10" t="s">
-        <v>87</v>
+        <v>106</v>
+      </c>
+      <c r="U10" t="s">
+        <v>35</v>
+      </c>
+      <c r="V10" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10" t="s">
+        <v>35</v>
+      </c>
+      <c r="X10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:20">
+    <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="2">
+        <v>109</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
       </c>
       <c r="H11" s="2">
         <v>0.35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11">
+        <v>84</v>
+      </c>
+      <c r="M11" s="2">
         <v>1.1</v>
       </c>
       <c r="N11">
         <v>1.5</v>
       </c>
       <c r="O11" t="s">
-        <v>66</v>
-      </c>
-      <c r="P11" s="5">
+        <v>85</v>
+      </c>
+      <c r="P11">
         <v>2</v>
       </c>
-      <c r="Q11" s="6" t="s">
-        <v>104</v>
+      <c r="Q11" t="s">
+        <v>121</v>
       </c>
       <c r="R11" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="S11" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="T11" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U11" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" t="s">
+        <v>35</v>
+      </c>
+      <c r="X11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:20">
+    <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="2">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>95</v>
       </c>
       <c r="H12" s="2">
         <v>0.35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12">
+        <v>84</v>
+      </c>
+      <c r="M12" s="2">
         <v>1.1</v>
       </c>
       <c r="N12">
         <v>1.5</v>
       </c>
       <c r="O12" t="s">
-        <v>66</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>108</v>
+        <v>85</v>
+      </c>
+      <c r="P12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>125</v>
       </c>
       <c r="R12" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="S12" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="T12" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U12" t="s">
+        <v>35</v>
+      </c>
+      <c r="V12" t="s">
+        <v>35</v>
+      </c>
+      <c r="W12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1" spans="1:20">
+    <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>111</v>
+        <v>127</v>
+      </c>
+      <c r="B13" t="s">
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="2">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="G13" t="s">
+        <v>95</v>
       </c>
       <c r="H13" s="2">
         <v>1.5</v>
@@ -2233,54 +2518,72 @@
         <v>8</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13">
+        <v>86</v>
+      </c>
+      <c r="M13" s="2">
         <v>1</v>
       </c>
       <c r="N13">
         <v>1.2</v>
       </c>
       <c r="O13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" s="5">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>112</v>
+        <v>96</v>
+      </c>
+      <c r="P13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="S13" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="T13" t="s">
-        <v>80</v>
+        <v>97</v>
+      </c>
+      <c r="U13" t="s">
+        <v>98</v>
+      </c>
+      <c r="V13">
+        <v>0.5</v>
+      </c>
+      <c r="W13">
+        <v>1.75</v>
+      </c>
+      <c r="X13">
+        <v>0.6</v>
+      </c>
+      <c r="Y13">
+        <v>0.8</v>
+      </c>
+      <c r="Z13">
+        <v>1.5</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:20">
+    <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>115</v>
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="2">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G14" t="s">
+        <v>95</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2295,181 +2598,235 @@
         <v>5</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14">
+        <v>86</v>
+      </c>
+      <c r="M14" s="2">
         <v>1</v>
       </c>
       <c r="N14">
         <v>1.2</v>
       </c>
       <c r="O14" t="s">
-        <v>77</v>
-      </c>
-      <c r="P14" s="5">
+        <v>103</v>
+      </c>
+      <c r="P14">
         <v>3</v>
       </c>
-      <c r="Q14" s="6" t="s">
-        <v>116</v>
+      <c r="Q14" t="s">
+        <v>131</v>
       </c>
       <c r="R14" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="S14" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T14" t="s">
-        <v>87</v>
+        <v>106</v>
+      </c>
+      <c r="U14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" t="s">
+        <v>35</v>
+      </c>
+      <c r="X14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:20">
+    <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>119</v>
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="2">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
       </c>
       <c r="H15" s="2">
         <v>0.35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15">
+        <v>84</v>
+      </c>
+      <c r="M15" s="2">
         <v>1.1</v>
       </c>
       <c r="N15">
         <v>1.5</v>
       </c>
       <c r="O15" t="s">
-        <v>66</v>
-      </c>
-      <c r="P15" s="5">
+        <v>85</v>
+      </c>
+      <c r="P15">
         <v>2</v>
       </c>
-      <c r="Q15" s="6" t="s">
-        <v>120</v>
+      <c r="Q15" t="s">
+        <v>135</v>
       </c>
       <c r="R15" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="S15" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="T15" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U15" t="s">
+        <v>35</v>
+      </c>
+      <c r="V15" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" t="s">
+        <v>35</v>
+      </c>
+      <c r="X15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1" spans="1:20">
+    <row r="16" spans="1:26">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="2">
+        <v>138</v>
+      </c>
+      <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>95</v>
       </c>
       <c r="H16" s="2">
         <v>0.35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16">
+        <v>84</v>
+      </c>
+      <c r="M16" s="2">
         <v>1.1</v>
       </c>
       <c r="N16">
         <v>1.5</v>
       </c>
       <c r="O16" t="s">
-        <v>66</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>124</v>
+        <v>85</v>
+      </c>
+      <c r="P16" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>139</v>
       </c>
       <c r="R16" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="S16" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="T16" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U16" t="s">
+        <v>35</v>
+      </c>
+      <c r="V16" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" t="s">
+        <v>35</v>
+      </c>
+      <c r="X16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:20">
+    <row r="17" spans="1:26">
       <c r="A17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>127</v>
+        <v>141</v>
+      </c>
+      <c r="B17" t="s">
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="2">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>76</v>
+        <v>94</v>
+      </c>
+      <c r="G17" t="s">
+        <v>95</v>
       </c>
       <c r="H17" s="2">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2">
         <v>1</v>
@@ -2481,54 +2838,72 @@
         <v>8</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M17">
+        <v>86</v>
+      </c>
+      <c r="M17" s="2">
         <v>1</v>
       </c>
       <c r="N17">
         <v>1.2</v>
       </c>
       <c r="O17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P17" s="5">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>128</v>
+        <v>96</v>
+      </c>
+      <c r="P17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="S17" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="T17" t="s">
-        <v>80</v>
+        <v>97</v>
+      </c>
+      <c r="U17" t="s">
+        <v>98</v>
+      </c>
+      <c r="V17">
+        <v>0.5</v>
+      </c>
+      <c r="W17">
+        <v>1.25</v>
+      </c>
+      <c r="X17">
+        <v>0.6</v>
+      </c>
+      <c r="Y17">
+        <v>0.8</v>
+      </c>
+      <c r="Z17">
+        <v>1.5</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1" spans="1:20">
+    <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
+      </c>
+      <c r="B18" t="s">
+        <v>144</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E18" s="2">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>95</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2543,178 +2918,232 @@
         <v>5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M18">
+        <v>86</v>
+      </c>
+      <c r="M18" s="2">
         <v>1</v>
       </c>
       <c r="N18">
         <v>1.2</v>
       </c>
       <c r="O18" t="s">
-        <v>77</v>
-      </c>
-      <c r="P18" s="5">
+        <v>103</v>
+      </c>
+      <c r="P18">
         <v>3</v>
       </c>
-      <c r="Q18" s="6" t="s">
-        <v>132</v>
+      <c r="Q18" t="s">
+        <v>145</v>
       </c>
       <c r="R18" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="S18" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T18" t="s">
-        <v>87</v>
+        <v>106</v>
+      </c>
+      <c r="U18" t="s">
+        <v>35</v>
+      </c>
+      <c r="V18" t="s">
+        <v>35</v>
+      </c>
+      <c r="W18" t="s">
+        <v>35</v>
+      </c>
+      <c r="X18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="1:20">
+    <row r="19" spans="1:26">
       <c r="A19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>135</v>
+        <v>147</v>
+      </c>
+      <c r="B19" t="s">
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="2">
+        <v>109</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G19" t="s">
+        <v>95</v>
       </c>
       <c r="H19" s="2">
         <v>0.35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19">
+        <v>84</v>
+      </c>
+      <c r="M19" s="2">
         <v>1.1</v>
       </c>
       <c r="N19">
         <v>1.5</v>
       </c>
       <c r="O19" t="s">
-        <v>66</v>
-      </c>
-      <c r="P19" s="5">
+        <v>85</v>
+      </c>
+      <c r="P19">
         <v>2</v>
       </c>
-      <c r="Q19" s="6" t="s">
-        <v>136</v>
+      <c r="Q19" t="s">
+        <v>149</v>
       </c>
       <c r="R19" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="S19" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="T19" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U19" t="s">
+        <v>35</v>
+      </c>
+      <c r="V19" t="s">
+        <v>35</v>
+      </c>
+      <c r="W19" t="s">
+        <v>35</v>
+      </c>
+      <c r="X19" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:26">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="2">
+        <v>152</v>
+      </c>
+      <c r="E20">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+      <c r="G20" t="s">
+        <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20">
+        <v>84</v>
+      </c>
+      <c r="M20" s="2">
         <v>1.1</v>
       </c>
       <c r="N20">
         <v>1.5</v>
       </c>
       <c r="O20" t="s">
-        <v>66</v>
-      </c>
-      <c r="P20" s="5">
+        <v>85</v>
+      </c>
+      <c r="P20">
         <v>1</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>140</v>
+      <c r="Q20" t="s">
+        <v>153</v>
       </c>
       <c r="R20" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S20" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="T20" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="U20" t="s">
+        <v>35</v>
+      </c>
+      <c r="V20" t="s">
+        <v>35</v>
+      </c>
+      <c r="W20" t="s">
+        <v>35</v>
+      </c>
+      <c r="X20" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:20">
+    <row r="21" spans="1:26">
       <c r="A21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>142</v>
+        <v>154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E21" s="2">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>155</v>
+      </c>
+      <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="G21" t="s">
+        <v>95</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2729,35 +3158,56 @@
         <v>5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M21">
+        <v>86</v>
+      </c>
+      <c r="M21" s="2">
         <v>1</v>
       </c>
       <c r="N21">
         <v>1.2</v>
       </c>
       <c r="O21" t="s">
-        <v>77</v>
-      </c>
-      <c r="P21" s="5">
+        <v>103</v>
+      </c>
+      <c r="P21">
         <v>2</v>
       </c>
-      <c r="Q21" s="7" t="s">
-        <v>143</v>
+      <c r="Q21" t="s">
+        <v>156</v>
       </c>
       <c r="R21" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="S21" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T21" t="s">
-        <v>87</v>
+        <v>106</v>
+      </c>
+      <c r="U21" t="s">
+        <v>35</v>
+      </c>
+      <c r="V21" t="s">
+        <v>35</v>
+      </c>
+      <c r="W21" t="s">
+        <v>35</v>
+      </c>
+      <c r="X21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="S4:Z4 A1:Z3 S5 X5:Z5 S6:Z8 S9:T9 X9:Z9 E11:Q11 A11:C11 S10:Z12 A4:Q4 A5:G5 I5:Q5 A6:Q8 A9:G9 I9:Q9 A10:Q10 S13:T13 X13:Z13 S14:Z16 S17:T17 W17:Z17 S18:Z21 A12:Q16 A17:G17 I17:Q17 A18:Q21" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="184">
   <si>
     <t>职业ID</t>
   </si>
@@ -112,6 +112,27 @@
     <t>未命中停留秒</t>
   </si>
   <si>
+    <t>观察范围</t>
+  </si>
+  <si>
+    <t>距离优先级</t>
+  </si>
+  <si>
+    <t>目标价值模式</t>
+  </si>
+  <si>
+    <t>目标类型分数</t>
+  </si>
+  <si>
+    <t>特殊移动</t>
+  </si>
+  <si>
+    <t>攻击噪声值</t>
+  </si>
+  <si>
+    <t>噪声半径</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
@@ -190,6 +211,27 @@
     <t>Seconds a miss stays on the ground; default 1.5</t>
   </si>
   <si>
+    <t>COC observe+fog radius; empty/&lt;=0 -&gt; 2</t>
+  </si>
+  <si>
+    <t>prefer nearest|farthest; empty=nearest</t>
+  </si>
+  <si>
+    <t>high-to-low|ignore; empty=high-to-low</t>
+  </si>
+  <si>
+    <t>type;score|... ; empty=no types</t>
+  </si>
+  <si>
+    <t>0=no 1=yes; SpecialMove soldiers ignore SupportsSpecialMove AirWall (D-101)</t>
+  </si>
+  <si>
+    <t>D-102 0=none; &gt;0 AA HitConfirm noise</t>
+  </si>
+  <si>
+    <t>D-102 world XZ radius</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
@@ -268,6 +310,27 @@
     <t>ParabolaMissLingerSeconds</t>
   </si>
   <si>
+    <t>ObserveRange</t>
+  </si>
+  <si>
+    <t>DistancePriority</t>
+  </si>
+  <si>
+    <t>TargetValueMode</t>
+  </si>
+  <si>
+    <t>TargetTypeScores</t>
+  </si>
+  <si>
+    <t>SpecialMove</t>
+  </si>
+  <si>
+    <t>AttackNoiseValue</t>
+  </si>
+  <si>
+    <t>NoiseRadius</t>
+  </si>
+  <si>
     <t>Class_BaseWarrior</t>
   </si>
   <si>
@@ -304,70 +367,88 @@
     <t>HPPK_UI_Class_BaseWarrior</t>
   </si>
   <si>
+    <t>Attack1;1</t>
+  </si>
+  <si>
+    <t>优先最近</t>
+  </si>
+  <si>
+    <t>无视价值</t>
+  </si>
+  <si>
+    <t>敌方单位;2|可破坏障碍物;1</t>
+  </si>
+  <si>
+    <t>Class_BaseArcher</t>
+  </si>
+  <si>
+    <t>枯骨射手</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Agility</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_1|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>Parabola</t>
+  </si>
+  <si>
+    <t>Attack3;1</t>
+  </si>
+  <si>
+    <t>优先最远</t>
+  </si>
+  <si>
+    <t>敌方单位;1</t>
+  </si>
+  <si>
+    <t>Class_BaseMage</t>
+  </si>
+  <si>
+    <t>枯骨法师</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>App_0_20</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Class_BaseMage</t>
+  </si>
+  <si>
+    <t>Attack5;1</t>
+  </si>
+  <si>
+    <t>由大到小</t>
+  </si>
+  <si>
+    <t>Class_BaseRogue</t>
+  </si>
+  <si>
+    <t>枯骨刺客</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>App_0_30</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Class_BaseRogue</t>
+  </si>
+  <si>
     <t>Attack1;1|Attack2;1</t>
-  </si>
-  <si>
-    <t>Class_BaseArcher</t>
-  </si>
-  <si>
-    <t>枯骨射手</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>Agility</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_1|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
-  </si>
-  <si>
-    <t>Parabola</t>
-  </si>
-  <si>
-    <t>Attack3;1</t>
-  </si>
-  <si>
-    <t>Attack1;1</t>
-  </si>
-  <si>
-    <t>Class_BaseMage</t>
-  </si>
-  <si>
-    <t>枯骨法师</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>App_0_20</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Class_BaseMage</t>
-  </si>
-  <si>
-    <t>Attack5;1</t>
-  </si>
-  <si>
-    <t>Class_BaseRogue</t>
-  </si>
-  <si>
-    <t>枯骨刺客</t>
-  </si>
-  <si>
-    <t>刺客</t>
-  </si>
-  <si>
-    <t>App_0_30</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Class_BaseRogue</t>
   </si>
   <si>
     <t>Class_Warrior</t>
@@ -1130,9 +1211,9 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1518,15 +1599,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="18" max="18" width="24.3333333333333" customWidth="1"/>
+    <col min="19" max="19" width="16.75" customWidth="1"/>
     <col min="20" max="20" width="22.5" customWidth="1"/>
     <col min="21" max="21" width="17.8333333333333" customWidth="1"/>
+    <col min="28" max="28" width="11.8333333333333" customWidth="1"/>
+    <col min="29" max="29" width="15.5833333333333" customWidth="1"/>
+    <col min="30" max="30" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1605,203 +1690,266 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:26">
+    <row r="3" s="1" customFormat="1" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:33">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2">
         <v>0.35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M4" s="2">
         <v>1.1</v>
@@ -1810,63 +1958,84 @@
         <v>1.5</v>
       </c>
       <c r="O4" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P4" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="R4" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S4" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="T4" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="U4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z4" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA4">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:33">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
@@ -1881,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M5" s="2">
         <v>1</v>
@@ -1890,25 +2059,25 @@
         <v>1.2</v>
       </c>
       <c r="O5" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R5" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T5" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U5" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="V5">
         <v>0.5</v>
@@ -1925,28 +2094,49 @@
       <c r="Z5">
         <v>1.5</v>
       </c>
+      <c r="AA5">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:33">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -1961,7 +2151,7 @@
         <v>5</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M6" s="2">
         <v>1</v>
@@ -1970,78 +2160,99 @@
         <v>1.2</v>
       </c>
       <c r="O6" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P6">
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="R6" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="T6" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="U6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA6">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:33">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H7" s="2">
         <v>0.35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M7" s="2">
         <v>1.1</v>
@@ -2050,78 +2261,99 @@
         <v>1.5</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P7">
         <v>2</v>
       </c>
       <c r="Q7" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="R7" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="T7" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z7" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:33">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M8" s="2">
         <v>1.1</v>
@@ -2130,63 +2362,84 @@
         <v>1.5</v>
       </c>
       <c r="O8" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q8" t="s">
+        <v>141</v>
+      </c>
+      <c r="R8" t="s">
+        <v>142</v>
+      </c>
+      <c r="S8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T8" t="s">
+        <v>138</v>
+      </c>
+      <c r="U8" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" t="s">
+        <v>42</v>
+      </c>
+      <c r="X8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD8" t="s">
         <v>114</v>
       </c>
-      <c r="R8" t="s">
-        <v>115</v>
-      </c>
-      <c r="S8" t="s">
-        <v>89</v>
-      </c>
-      <c r="T8" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" t="s">
-        <v>35</v>
-      </c>
-      <c r="W8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>35</v>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:33">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G9" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H9" s="2">
         <v>3</v>
@@ -2201,7 +2454,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M9" s="2">
         <v>1</v>
@@ -2210,25 +2463,25 @@
         <v>1.2</v>
       </c>
       <c r="O9" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R9" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T9" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="V9">
         <v>0.5</v>
@@ -2245,28 +2498,49 @@
       <c r="Z9">
         <v>1.5</v>
       </c>
+      <c r="AA9">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:33">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -2281,7 +2555,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M10" s="2">
         <v>1</v>
@@ -2290,75 +2564,96 @@
         <v>1.2</v>
       </c>
       <c r="O10" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P10">
         <v>3</v>
       </c>
       <c r="Q10" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="R10" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="S10" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="T10" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="U10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z10" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA10">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:33">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H11" s="2">
         <v>0.35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M11" s="2">
         <v>1.1</v>
@@ -2367,78 +2662,99 @@
         <v>1.5</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P11">
         <v>2</v>
       </c>
       <c r="Q11" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="R11" t="s">
+        <v>149</v>
+      </c>
+      <c r="S11" t="s">
+        <v>137</v>
+      </c>
+      <c r="T11" t="s">
+        <v>138</v>
+      </c>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="s">
         <v>122</v>
       </c>
-      <c r="S11" t="s">
-        <v>111</v>
-      </c>
-      <c r="T11" t="s">
-        <v>90</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" t="s">
-        <v>35</v>
-      </c>
-      <c r="W11" t="s">
-        <v>35</v>
-      </c>
-      <c r="X11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>35</v>
+      <c r="AC11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:33">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H12" s="2">
         <v>0.35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M12" s="2">
         <v>1.1</v>
@@ -2447,63 +2763,84 @@
         <v>1.5</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P12" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q12" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="R12" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="S12" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="T12" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z12" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:33">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2">
         <v>1.5</v>
@@ -2518,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M13" s="2">
         <v>1</v>
@@ -2527,25 +2864,25 @@
         <v>1.2</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R13" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T13" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U13" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="V13">
         <v>0.5</v>
@@ -2562,28 +2899,49 @@
       <c r="Z13">
         <v>1.5</v>
       </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <v>4</v>
+      </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:33">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -2598,7 +2956,7 @@
         <v>5</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M14" s="2">
         <v>1</v>
@@ -2607,78 +2965,99 @@
         <v>1.2</v>
       </c>
       <c r="O14" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P14">
         <v>3</v>
       </c>
       <c r="Q14" t="s">
+        <v>158</v>
+      </c>
+      <c r="R14" t="s">
+        <v>159</v>
+      </c>
+      <c r="S14" t="s">
+        <v>130</v>
+      </c>
+      <c r="T14" t="s">
         <v>131</v>
       </c>
-      <c r="R14" t="s">
+      <c r="U14" t="s">
+        <v>42</v>
+      </c>
+      <c r="V14" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" t="s">
+        <v>42</v>
+      </c>
+      <c r="X14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC14" t="s">
         <v>132</v>
       </c>
-      <c r="S14" t="s">
-        <v>105</v>
-      </c>
-      <c r="T14" t="s">
-        <v>106</v>
-      </c>
-      <c r="U14" t="s">
-        <v>35</v>
-      </c>
-      <c r="V14" t="s">
-        <v>35</v>
-      </c>
-      <c r="W14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>35</v>
+      <c r="AD14" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:33">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="E15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H15" s="2">
         <v>0.35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M15" s="2">
         <v>1.1</v>
@@ -2687,78 +3066,99 @@
         <v>1.5</v>
       </c>
       <c r="O15" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P15">
         <v>2</v>
       </c>
       <c r="Q15" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="R15" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="S15" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="T15" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:33">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H16" s="2">
         <v>0.35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M16" s="2">
         <v>1.1</v>
@@ -2767,63 +3167,84 @@
         <v>1.5</v>
       </c>
       <c r="O16" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="Q16" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="R16" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="S16" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="T16" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z16" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:33">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H17" s="2">
         <v>3</v>
@@ -2838,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M17" s="2">
         <v>1</v>
@@ -2847,25 +3268,25 @@
         <v>1.2</v>
       </c>
       <c r="O17" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R17" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T17" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="U17" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="V17">
         <v>0.5</v>
@@ -2882,28 +3303,49 @@
       <c r="Z17">
         <v>1.5</v>
       </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:33">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -2918,7 +3360,7 @@
         <v>5</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M18" s="2">
         <v>1</v>
@@ -2927,78 +3369,99 @@
         <v>1.2</v>
       </c>
       <c r="O18" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P18">
         <v>3</v>
       </c>
       <c r="Q18" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="R18" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="S18" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="T18" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="U18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z18" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA18">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>2</v>
+      </c>
+      <c r="AG18">
+        <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:33">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2">
         <v>0.35</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M19" s="2">
         <v>1.1</v>
@@ -3007,78 +3470,99 @@
         <v>1.5</v>
       </c>
       <c r="O19" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P19">
         <v>2</v>
       </c>
       <c r="Q19" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="R19" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="S19" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="T19" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y19" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z19" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:33">
       <c r="A20" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="E20">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G20" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="M20" s="2">
         <v>1.1</v>
@@ -3087,63 +3571,84 @@
         <v>1.5</v>
       </c>
       <c r="O20" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="P20">
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="R20" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="T20" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="U20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y20" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z20" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA20">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:33">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="E21">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -3158,7 +3663,7 @@
         <v>5</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M21" s="2">
         <v>1</v>
@@ -3167,47 +3672,68 @@
         <v>1.2</v>
       </c>
       <c r="O21" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="P21">
         <v>2</v>
       </c>
       <c r="Q21" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="R21" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="S21" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="T21" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="U21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="V21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="X21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y21" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Z21" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>2</v>
+      </c>
+      <c r="AG21">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="S4:Z4 A1:Z3 S5 X5:Z5 S6:Z8 S9:T9 X9:Z9 E11:Q11 A11:C11 S10:Z12 A4:Q4 A5:G5 I5:Q5 A6:Q8 A9:G9 I9:Q9 A10:Q10 S13:T13 X13:Z13 S14:Z16 S17:T17 W17:Z17 S18:Z21 A12:Q16 A17:G17 I17:Q17 A18:Q21" numberStoredAsText="1"/>
+    <ignoredError sqref="A18:Q21 I17:Q17 A17:G17 A12:Q16 S18:Z21 W17:Z17 S17:T17 S14:Z15 S16 U16:Z16 X13:Z13 S13:T13 A10:Q10 I9:Q9 A9:G9 A6:Q8 I5:Q5 A5:G5 A4:Q4 S10:Z12 A11:C11 E11:Q11 X9:Z9 S9:T9 S6:Z8 X5:Z5 S4:S5 A1:Z2 A3:G3 I3:Z3 U4:Z4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>